--- a/docs/3/project-management/Учебный_план_Управление_проектами.xlsx
+++ b/docs/3/project-management/Учебный_план_Управление_проектами.xlsx
@@ -160,7 +160,7 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Минуты</t>
+          <t xml:space="preserve">Часы</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
@@ -191,7 +191,7 @@
         </is>
       </c>
       <c r="D6" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
@@ -221,7 +221,7 @@
         </is>
       </c>
       <c r="D7" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
@@ -251,7 +251,7 @@
         </is>
       </c>
       <c r="D8" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
@@ -281,7 +281,7 @@
         </is>
       </c>
       <c r="D9" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
@@ -311,7 +311,7 @@
         </is>
       </c>
       <c r="D10" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
@@ -341,7 +341,7 @@
         </is>
       </c>
       <c r="D11" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
@@ -371,7 +371,7 @@
         </is>
       </c>
       <c r="D12" s="6">
-        <v>180</v>
+        <v>4</v>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
@@ -401,7 +401,7 @@
         </is>
       </c>
       <c r="D13" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
@@ -431,7 +431,7 @@
         </is>
       </c>
       <c r="D14" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
@@ -461,7 +461,7 @@
         </is>
       </c>
       <c r="D15" s="6">
-        <v>180</v>
+        <v>4</v>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
@@ -491,7 +491,7 @@
         </is>
       </c>
       <c r="D16" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
@@ -521,7 +521,7 @@
         </is>
       </c>
       <c r="D17" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
@@ -551,7 +551,7 @@
         </is>
       </c>
       <c r="D18" s="6">
-        <v>180</v>
+        <v>4</v>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
@@ -581,7 +581,7 @@
         </is>
       </c>
       <c r="D19" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
@@ -611,7 +611,7 @@
         </is>
       </c>
       <c r="D20" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="D21" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
@@ -671,7 +671,7 @@
         </is>
       </c>
       <c r="D22" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
@@ -701,7 +701,7 @@
         </is>
       </c>
       <c r="D23" s="6">
-        <v>1800</v>
+        <v>40</v>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>

--- a/docs/3/project-management/Учебный_план_Управление_проектами.xlsx
+++ b/docs/3/project-management/Учебный_план_Управление_проектами.xlsx
@@ -204,7 +204,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="45" customHeight="1">
+    <row r="7" ht="60" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
@@ -212,85 +212,85 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
+          <t xml:space="preserve">Лекция</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Лекция 2. Жизненный цикл проекта</t>
+        </is>
+      </c>
+      <c r="D7" s="6">
+        <v>2</v>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Фазы от инициации до закрытия, ворота между ними и выбор между водопадной и итеративной моделью: где проект получает право двигаться дальше и где дешевле всего исправить ошибку.</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Фазы проекта, Ворота, Водопад, Итерации</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="45" customHeight="1">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Лекция</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Лекция 3. Инициация и устав</t>
+        </is>
+      </c>
+      <c r="D8" s="6">
+        <v>2</v>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Как проект получает право на существование: бизнес-обоснование, устав, допущения и ограничения, решение идти или не идти, подпись спонсора.</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Бизнес-обоснование, Устав, Допущения, Ограничения</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="45" customHeight="1">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
           <t xml:space="preserve">Практика</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">Практика 1. Устав проекта</t>
         </is>
       </c>
-      <c r="D7" s="6">
-        <v>2</v>
-      </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Студент собирает устав учебного проекта: цель, границы, результаты, вехи, бюджет, роли и критерии приёмки, затем проверяет документ по чек-листу.</t>
-        </is>
-      </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="D9" s="6">
+        <v>2</v>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Вы собираете устав учебного проекта: цель, границы, результаты, вехи, бюджет, роли и критерии приёмки, затем проверяете документ по чек-листу.</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">Устав проекта, Границы, Вехи, Критерии приёмки</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="60" customHeight="1">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Лекция</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Лекция 2. Жизненный цикл проекта</t>
-        </is>
-      </c>
-      <c r="D8" s="6">
-        <v>2</v>
-      </c>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Фазы от инициации до закрытия, ворота между ними и выбор между водопадной и итеративной моделью: где проект получает право двигаться дальше и где дешевле всего исправить ошибку.</t>
-        </is>
-      </c>
-      <c r="F8" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Фазы проекта, Ворота, Водопад, Итерации</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="60" customHeight="1">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Практика</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Практика 2. Стейкхолдеры</t>
-        </is>
-      </c>
-      <c r="D9" s="6">
-        <v>2</v>
-      </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Студент строит реестр заинтересованных сторон учебной ИС, раскладывает их по карте власти и интереса, выбирает стратегию вовлечения и распределяет ответственность по RACI.</t>
-        </is>
-      </c>
-      <c r="F9" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Реестр стейкхолдеров, Власть и интерес, Стратегии вовлечения, RACI</t>
         </is>
       </c>
     </row>
@@ -307,7 +307,7 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 3. Инициация и устав</t>
+          <t xml:space="preserve">Лекция 4. Заинтересованные стороны</t>
         </is>
       </c>
       <c r="D10" s="6">
@@ -315,16 +315,16 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как проект получает право на существование: бизнес-обоснование, устав, допущения и ограничения, решение идти или не идти, подпись спонсора.</t>
+          <t xml:space="preserve">Стейкхолдеры, их власть, интерес и влияние на проект: карта сторон, стратегии работы, конфликт интересов и план вовлечения на весь срок.</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Бизнес-обоснование, Устав, Допущения, Ограничения</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="45" customHeight="1">
+          <t xml:space="preserve">Карта стейкхолдеров, Влияние, Вовлечение, Конфликт интересов</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="60" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">6</t>
@@ -332,12 +332,12 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция</t>
+          <t xml:space="preserve">Практика</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 4. Заинтересованные стороны</t>
+          <t xml:space="preserve">Практика 2. Стейкхолдеры</t>
         </is>
       </c>
       <c r="D11" s="6">
@@ -345,72 +345,72 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Стейкхолдеры, их власть, интерес и влияние на проект: карта сторон, стратегии работы, конфликт интересов и план вовлечения на весь срок.</t>
+          <t xml:space="preserve">Вы строите реестр заинтересованных сторон учебной ИС, раскладываете их по карте власти и интереса, выбираете стратегию вовлечения и распределяете ответственность по RACI.</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Карта стейкхолдеров, Влияние, Вовлечение, Конфликт интересов</t>
+          <t xml:space="preserve">Реестр стейкхолдеров, Власть и интерес, Стратегии вовлечения, RACI</t>
         </is>
       </c>
     </row>
     <row r="12" ht="60" customHeight="1">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">7-8</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика</t>
+          <t xml:space="preserve">Лекция</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика 3. WBS и диаграмма Ганта в Excel</t>
+          <t xml:space="preserve">Лекция 5. WBS и расписание</t>
         </is>
       </c>
       <c r="D12" s="6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Совмещённая практика: декомпозиция результата до пакетов работ, словарь WBS, зависимости и критический путь, затем диаграмма Ганта в Excel с условным форматированием и базовым планом.</t>
+          <t xml:space="preserve">Декомпозиция до пакетов, оценки по трём точкам, зависимости, прямой и обратный проход, резерв и критический путь: как из списка работ получается проверяемое расписание.</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">WBS, Словарь работ, Зависимости, Диаграмма Ганта</t>
+          <t xml:space="preserve">WBS, Оценка PERT, Сеть работ, Критический путь</t>
         </is>
       </c>
     </row>
     <row r="13" ht="60" customHeight="1">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">8-9</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция</t>
+          <t xml:space="preserve">Практика</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 5. WBS и расписание</t>
+          <t xml:space="preserve">Практика 3. WBS и диаграмма Ганта в Excel</t>
         </is>
       </c>
       <c r="D13" s="6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Декомпозиция до пакетов, оценки по трём точкам, зависимости, прямой и обратный проход, резерв и критический путь: как из списка работ получается проверяемое расписание.</t>
+          <t xml:space="preserve">Совмещённая практика: декомпозиция результата до пакетов работ, словарь WBS, зависимости и критический путь, затем диаграмма Ганта в Excel с условным форматированием и базовым планом.</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">WBS, Оценка PERT, Сеть работ, Критический путь</t>
+          <t xml:space="preserve">WBS, Словарь работ, Зависимости, Диаграмма Ганта</t>
         </is>
       </c>
     </row>
@@ -444,63 +444,63 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="45" customHeight="1">
+    <row r="15" ht="60" customHeight="1">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">11-12</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
+          <t xml:space="preserve">Лекция</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Лекция 7. Риски</t>
+        </is>
+      </c>
+      <c r="D15" s="6">
+        <v>2</v>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Риск как событие с вероятностью и последствием: идентификация, качественная и количественная оценка, EMV, стратегии реагирования и триггеры, которые включают план.</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Идентификация рисков, Матрица рисков, EMV, Реагирование</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="45" customHeight="1">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12-13</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
           <t xml:space="preserve">Практика</t>
         </is>
       </c>
-      <c r="C15" s="5" t="inlineStr">
+      <c r="C16" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">Практика 4. Бюджет и риски</t>
         </is>
       </c>
-      <c r="D15" s="6">
+      <c r="D16" s="6">
         <v>4</v>
       </c>
-      <c r="E15" s="5" t="inlineStr">
+      <c r="E16" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">Совмещённая практика: смета и базовый бюджет проекта, затем реестр рисков с вероятностью, влиянием, EMV, стратегиями реагирования и резервом.</t>
         </is>
       </c>
-      <c r="F15" s="5" t="inlineStr">
+      <c r="F16" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">Смета, Базовый бюджет, Реестр рисков, EMV</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="60" customHeight="1">
-      <c r="A16" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">13</t>
-        </is>
-      </c>
-      <c r="B16" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Лекция</t>
-        </is>
-      </c>
-      <c r="C16" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Лекция 7. Риски</t>
-        </is>
-      </c>
-      <c r="D16" s="6">
-        <v>2</v>
-      </c>
-      <c r="E16" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Риск как событие с вероятностью и последствием: идентификация, качественная и количественная оценка, EMV, стратегии реагирования и триггеры, которые включают план.</t>
-        </is>
-      </c>
-      <c r="F16" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Идентификация рисков, Матрица рисков, EMV, Реагирование</t>
         </is>
       </c>
     </row>
@@ -537,60 +537,60 @@
     <row r="18" ht="45" customHeight="1">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">15-16</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика</t>
+          <t xml:space="preserve">Лекция</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика 5. План качества и план коммуникаций</t>
+          <t xml:space="preserve">Лекция 9. Коммуникации и команда</t>
         </is>
       </c>
       <c r="D18" s="6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Совмещённая практика: критерии качества и план проверок для учебной ИС, затем матрица коммуникаций с адресатами, формой, частотой и ответственным.</t>
+          <t xml:space="preserve">Сообщение, канал, шум и обратная связь; число каналов в команде, стадии развития группы, RACI, мотивация и разбор конфликта без поиска виноватого.</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Критерии качества, План проверок, Матрица коммуникаций, Эскалация</t>
+          <t xml:space="preserve">Модель коммуникации, Каналы, Стадии команды, Конфликт</t>
         </is>
       </c>
     </row>
     <row r="19" ht="45" customHeight="1">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">16-17</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция</t>
+          <t xml:space="preserve">Практика</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 9. Коммуникации и команда</t>
+          <t xml:space="preserve">Практика 5. План качества и план коммуникаций</t>
         </is>
       </c>
       <c r="D19" s="6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сообщение, канал, шум и обратная связь; число каналов в команде, стадии развития группы, RACI, мотивация и разбор конфликта без поиска виноватого.</t>
+          <t xml:space="preserve">Совмещённая практика: критерии качества и план проверок для учебной ИС, затем матрица коммуникаций с адресатами, формой, частотой и ответственным.</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Модель коммуникации, Каналы, Стадии команды, Конфликт</t>
+          <t xml:space="preserve">Критерии качества, План проверок, Матрица коммуникаций, Эскалация</t>
         </is>
       </c>
     </row>
@@ -602,12 +602,12 @@
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика</t>
+          <t xml:space="preserve">Лекция</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика 6. Scrum-доска</t>
+          <t xml:space="preserve">Лекция 10. Agile, Scrum и завершение</t>
         </is>
       </c>
       <c r="D20" s="6">
@@ -615,12 +615,12 @@
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Студент собирает продуктовый бэклог из пользовательских историй, оценивает их в story points, планирует спринт, ведёт доску и строит график сгорания.</t>
+          <t xml:space="preserve">Ценности Agile, роли и события Scrum, Kanban и гибридные схемы, а затем закрытие проекта: приёмка, передача, извлечённые уроки, архив и оценка выгоды.</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Product backlog, User story, Story points, Burndown</t>
+          <t xml:space="preserve">Agile, Scrum, Kanban, Закрытие проекта</t>
         </is>
       </c>
     </row>
@@ -632,12 +632,12 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция</t>
+          <t xml:space="preserve">Практика</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 10. Agile, Scrum и завершение</t>
+          <t xml:space="preserve">Практика 6. Scrum-доска</t>
         </is>
       </c>
       <c r="D21" s="6">
@@ -645,12 +645,12 @@
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ценности Agile, роли и события Scrum, Kanban и гибридные схемы, а затем закрытие проекта: приёмка, передача, извлечённые уроки, архив и оценка выгоды.</t>
+          <t xml:space="preserve">Вы собираете продуктовый бэклог из пользовательских историй, оцениваете их в story points, планируете спринт, ведёте доску и строите график сгорания.</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Agile, Scrum, Kanban, Закрытие проекта</t>
+          <t xml:space="preserve">Product backlog, User story, Story points, Burndown</t>
         </is>
       </c>
     </row>
@@ -675,7 +675,7 @@
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Итоговая защита: студент показывает пакет проекта, сравнивает план с фактом, объясняет решения по срокам, бюджету и рискам и отвечает на вопросы комиссии.</t>
+          <t xml:space="preserve">Итоговая защита: вы показываете пакет проекта, сравниваете план с фактом, объясняете решения по срокам, бюджету и рискам и отвечаете на вопросы комиссии.</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
